--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -3,24 +3,25 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SathishReddy Sandhi\SeleniumAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9942B1D7-3B81-4C87-944B-6DB53D4A4507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D43A39F-BBF0-4140-B8BE-DA360D2B1864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="2" r:id="rId1"/>
     <sheet name="Cart" sheetId="3" r:id="rId2"/>
     <sheet name="Payment" sheetId="4" r:id="rId3"/>
     <sheet name="Order" sheetId="5" r:id="rId4"/>
+    <sheet name="Results" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,60 +29,73 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>ProductName</t>
   </si>
   <si>
-    <t>ProductCount</t>
-  </si>
-  <si>
-    <t>CerditCardNumber</t>
-  </si>
-  <si>
-    <t>exp Month</t>
-  </si>
-  <si>
-    <t>exp Date</t>
-  </si>
-  <si>
     <t>CVV</t>
   </si>
   <si>
-    <t>NameOnCard</t>
-  </si>
-  <si>
     <t>Country</t>
   </si>
   <si>
     <t>iphone 13 pro</t>
   </si>
   <si>
-    <t>1234567890987650</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
     <t>Sathish Reddy</t>
   </si>
   <si>
     <t>India</t>
   </si>
   <si>
-    <t>1</t>
+    <t>ExpectedCartCount</t>
+  </si>
+  <si>
+    <t>CardNumber</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>ExpectedQty</t>
+  </si>
+  <si>
+    <t>ZARA COAT 3</t>
+  </si>
+  <si>
+    <t>Sathish Reddy Sandhi</t>
+  </si>
+  <si>
+    <t>1234567898765432</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>E2ETest</t>
+  </si>
+  <si>
+    <t>CompletedFlow</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Cart.goToCheckout</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -91,12 +105,32 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -111,9 +145,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,27 +433,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2D4A01-FD8A-4C00-8AEF-6100DA0E02DE}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.1796875"/>
+    <col min="2" max="2" customWidth="true" width="23.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -424,23 +471,34 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334CF848-C880-4642-954D-864DF5E51C2D}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="19.90625"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -451,53 +509,73 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2AF52E-5086-43AC-9E41-3304A02A9C8C}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.26953125" customWidth="1"/>
-    <col min="2" max="2" width="12.6328125" customWidth="1"/>
-    <col min="5" max="5" width="23.1796875" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="23.81640625"/>
+    <col min="2" max="2" customWidth="true" width="12.6328125"/>
+    <col min="5" max="5" customWidth="true" width="23.1796875"/>
+    <col min="6" max="6" customWidth="true" width="13.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1">
+        <v>274</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D3" s="1">
+        <v>294</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>14</v>
+      <c r="F3" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -507,27 +585,89 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E14915E-E896-4209-8E48-035EA63E22E1}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.1796875" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="16.1796875"/>
+    <col min="2" max="2" customWidth="true" width="36.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FAC67C-2142-481E-8C57-BF49024F7BB1}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="6">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SathishReddy Sandhi\SeleniumAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D43A39F-BBF0-4140-B8BE-DA360D2B1864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B21351-D445-4ACC-B24F-292D7CEB8FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="2" r:id="rId1"/>
-    <sheet name="Cart" sheetId="3" r:id="rId2"/>
-    <sheet name="Payment" sheetId="4" r:id="rId3"/>
-    <sheet name="Order" sheetId="5" r:id="rId4"/>
-    <sheet name="Results" sheetId="6" r:id="rId5"/>
+    <sheet name="Results" sheetId="8" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
+    <sheet name="Cart" sheetId="3" r:id="rId3"/>
+    <sheet name="Payment" sheetId="4" r:id="rId4"/>
+    <sheet name="Order" sheetId="5" r:id="rId5"/>
+    <sheet name="shipmnent" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="36">
   <si>
     <t>ProductName</t>
   </si>
@@ -40,62 +41,113 @@
     <t>Country</t>
   </si>
   <si>
+    <t>Sathish Reddy</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>ExpectedCartCount</t>
+  </si>
+  <si>
+    <t>CardNumber</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>ExpectedQty</t>
+  </si>
+  <si>
+    <t>Sathish Reddy Sandhi</t>
+  </si>
+  <si>
+    <t>1234567898765432</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>landmark</t>
+  </si>
+  <si>
+    <t>vlmp</t>
+  </si>
+  <si>
+    <t>hanuman temple</t>
+  </si>
+  <si>
+    <t>1234564898765437</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Devender Reddy</t>
+  </si>
+  <si>
+    <t>E2ETest</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Cart.goToCheckout</t>
+  </si>
+  <si>
+    <t>ZARA COAT 3</t>
+  </si>
+  <si>
+    <t>TestCaseName</t>
+  </si>
+  <si>
+    <t>StepName</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Dashboard.addProductToCart</t>
+  </si>
+  <si>
     <t>iphone 13 pro</t>
   </si>
   <si>
-    <t>Sathish Reddy</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>ExpectedCartCount</t>
-  </si>
-  <si>
-    <t>CardNumber</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>ExpectedQty</t>
-  </si>
-  <si>
-    <t>ZARA COAT 3</t>
-  </si>
-  <si>
-    <t>Sathish Reddy Sandhi</t>
-  </si>
-  <si>
-    <t>1234567898765432</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>E2ETest</t>
-  </si>
-  <si>
-    <t>CompletedFlow</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Cart.goToCheckout</t>
+    <t>Clothes</t>
+  </si>
+  <si>
+    <t>Execution</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Dashboard.goToCartPage</t>
+  </si>
+  <si>
+    <t>Completed Execution</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -113,13 +165,8 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="17"/>
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
     <fill>
@@ -128,8 +175,13 @@
       </patternFill>
     </fill>
     <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="17"/>
       </patternFill>
     </fill>
   </fills>
@@ -145,14 +197,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,11 +535,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2D4A01-FD8A-4C00-8AEF-6100DA0E02DE}">
-  <dimension ref="A1:B3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4687A51-E3F6-4959-AD9A-99F0B4444C26}">
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="14.1796875"/>
+    <col min="2" max="2" customWidth="true" width="29.90625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s" s="52">
+        <v>33</v>
+      </c>
+      <c r="D2" s="53" t="n">
+        <v>46107.07114574074</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s" s="54">
+        <v>33</v>
+      </c>
+      <c r="D3" s="55" t="n">
+        <v>46107.07139671296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s" s="56">
+        <v>33</v>
+      </c>
+      <c r="D4" s="57" t="n">
+        <v>46107.071665972224</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2D4A01-FD8A-4C00-8AEF-6100DA0E02DE}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="37.54296875"/>
     <col min="2" max="2" customWidth="true" width="23.08984375"/>
   </cols>
   <sheetData>
@@ -445,33 +617,42 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
+        <v>30</v>
+      </c>
+      <c r="B2" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" s="0">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334CF848-C880-4642-954D-864DF5E51C2D}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="19.90625"/>
@@ -482,22 +663,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
+        <v>30</v>
+      </c>
+      <c r="B2" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" s="0">
         <v>1</v>
       </c>
     </row>
@@ -507,9 +696,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2AF52E-5086-43AC-9E41-3304A02A9C8C}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="23.81640625"/>
@@ -520,19 +709,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s" s="0">
         <v>9</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>10</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>2</v>
@@ -540,7 +729,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1">
         <v>12</v>
@@ -552,18 +741,18 @@
         <v>274</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s" s="0">
         <v>4</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>10</v>
@@ -572,10 +761,30 @@
         <v>294</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>5</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1">
+        <v>934</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -583,9 +792,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E14915E-E896-4209-8E48-035EA63E22E1}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="16.1796875"/>
@@ -597,22 +806,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
+        <v>30</v>
+      </c>
+      <c r="B2" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" s="0">
         <v>1</v>
       </c>
     </row>
@@ -622,52 +839,44 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FAC67C-2142-481E-8C57-BF49024F7BB1}">
-  <dimension ref="A1:C5"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8EAE46-4B76-4386-9505-380624A1252D}">
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="22.54296875"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s" s="0">
         <v>16</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
         <v>16</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="C3" t="s" s="4">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
         <v>16</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>17</v>
-      </c>
-      <c r="C4" t="s" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s" s="6">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SathishReddy Sandhi\SeleniumAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B21351-D445-4ACC-B24F-292D7CEB8FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2A19D8-0574-4660-A5BF-B2D67A58DE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="8" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
   <si>
     <t>ProductName</t>
   </si>
@@ -95,49 +95,34 @@
     <t>Devender Reddy</t>
   </si>
   <si>
+    <t>ZARA COAT 3</t>
+  </si>
+  <si>
+    <t>TestCaseName</t>
+  </si>
+  <si>
+    <t>StepName</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>iphone 13 pro</t>
+  </si>
+  <si>
+    <t>Clothes</t>
+  </si>
+  <si>
     <t>E2ETest</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>Cart.goToCheckout</t>
-  </si>
-  <si>
-    <t>ZARA COAT 3</t>
-  </si>
-  <si>
-    <t>TestCaseName</t>
-  </si>
-  <si>
-    <t>StepName</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Dashboard.addProductToCart</t>
-  </si>
-  <si>
-    <t>iphone 13 pro</t>
-  </si>
-  <si>
-    <t>Clothes</t>
-  </si>
-  <si>
-    <t>Execution</t>
+    <t>Completed Execution</t>
   </si>
   <si>
     <t>PASS</t>
-  </si>
-  <si>
-    <t>Dashboard.goToCartPage</t>
-  </si>
-  <si>
-    <t>Completed Execution</t>
   </si>
 </sst>
 </file>
@@ -157,7 +142,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,21 +151,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="17"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
@@ -197,64 +172,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
@@ -536,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4687A51-E3F6-4959-AD9A-99F0B4444C26}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="29.90625"/>
@@ -544,58 +469,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s" s="52">
-        <v>33</v>
-      </c>
-      <c r="D2" s="53" t="n">
-        <v>46107.07114574074</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s" s="54">
-        <v>33</v>
-      </c>
-      <c r="D3" s="55" t="n">
-        <v>46107.07139671296</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s" s="56">
-        <v>33</v>
-      </c>
-      <c r="D4" s="57" t="n">
-        <v>46107.071665972224</v>
+        <v>29</v>
+      </c>
+      <c r="C2" t="s" s="6">
+        <v>30</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>46107.51998511574</v>
       </c>
     </row>
   </sheetData>
@@ -622,7 +519,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2" s="0">
         <v>1</v>
@@ -630,7 +527,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -638,7 +535,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B4" s="0">
         <v>1</v>
@@ -668,7 +565,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2" s="0">
         <v>1</v>
@@ -676,7 +573,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -684,7 +581,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B4" s="0">
         <v>1</v>
@@ -811,7 +708,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2" s="0">
         <v>1</v>
@@ -819,7 +716,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -827,7 +724,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B4" s="0">
         <v>1</v>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="33">
   <si>
     <t>ProductName</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>PASS</t>
+  </si>
+  <si>
+    <t>UnknownLocation</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
 </sst>
 </file>
@@ -142,7 +148,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,6 +165,16 @@
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -172,11 +188,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -461,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4687A51-E3F6-4959-AD9A-99F0B4444C26}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="29.90625"/>
@@ -488,11 +518,39 @@
       <c r="B2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="C2" t="s" s="6">
+      <c r="C2" t="s" s="16">
         <v>30</v>
       </c>
-      <c r="D2" s="7" t="n">
-        <v>46107.51998511574</v>
+      <c r="D2" s="17" t="n">
+        <v>46107.54341019676</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s" s="18">
+        <v>30</v>
+      </c>
+      <c r="D3" s="19" t="n">
+        <v>46107.54367148148</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s" s="20">
+        <v>30</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>46107.54393357639</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SathishReddy Sandhi\SeleniumAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2A19D8-0574-4660-A5BF-B2D67A58DE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCED712A-2653-4074-940B-E9F8AF2C7DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="Cart" sheetId="3" r:id="rId3"/>
     <sheet name="Payment" sheetId="4" r:id="rId4"/>
     <sheet name="Order" sheetId="5" r:id="rId5"/>
-    <sheet name="shipmnent" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="32">
   <si>
     <t>ProductName</t>
   </si>
@@ -74,18 +73,6 @@
     <t>09</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>landmark</t>
-  </si>
-  <si>
-    <t>vlmp</t>
-  </si>
-  <si>
-    <t>hanuman temple</t>
-  </si>
-  <si>
     <t>1234564898765437</t>
   </si>
   <si>
@@ -125,10 +112,19 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>UnknownLocation</t>
-  </si>
-  <si>
-    <t>FAIL</t>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>TC_01_iphone 13 pro</t>
+  </si>
+  <si>
+    <t>TC_02_ZARACOAT3</t>
+  </si>
+  <si>
+    <t>TC_03_Clothes</t>
   </si>
 </sst>
 </file>
@@ -148,7 +144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,16 +161,6 @@
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -188,17 +174,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -499,58 +479,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s" s="16">
-        <v>30</v>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>46107.54341019676</v>
+        <v>25</v>
+      </c>
+      <c r="C2" t="s" s="10">
+        <v>26</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>46107.58985373843</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s" s="18">
-        <v>30</v>
-      </c>
-      <c r="D3" s="19" t="n">
-        <v>46107.54367148148</v>
+        <v>25</v>
+      </c>
+      <c r="C3" t="s" s="12">
+        <v>26</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>46107.590114976854</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s" s="20">
-        <v>30</v>
-      </c>
-      <c r="D4" s="21" t="n">
-        <v>46107.54393357639</v>
+        <v>25</v>
+      </c>
+      <c r="C4" t="s" s="14">
+        <v>26</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>46107.59039252315</v>
       </c>
     </row>
   </sheetData>
@@ -560,42 +540,67 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2D4A01-FD8A-4C00-8AEF-6100DA0E02DE}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="37.54296875"/>
-    <col min="2" max="2" customWidth="true" width="23.08984375"/>
+    <col min="1" max="1" customWidth="true" width="15.36328125"/>
+    <col min="3" max="3" customWidth="true" width="37.54296875"/>
+    <col min="4" max="4" customWidth="true" width="23.08984375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D2" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B4" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="D4" s="0">
         <v>1</v>
       </c>
     </row>
@@ -607,41 +612,53 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334CF848-C880-4642-954D-864DF5E51C2D}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="19.90625"/>
+    <col min="3" max="3" customWidth="true" width="19.90625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B4" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C4" s="0">
         <v>1</v>
       </c>
     </row>
@@ -653,92 +670,104 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2AF52E-5086-43AC-9E41-3304A02A9C8C}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="23.81640625"/>
-    <col min="2" max="2" customWidth="true" width="12.6328125"/>
-    <col min="5" max="5" customWidth="true" width="23.1796875"/>
-    <col min="6" max="6" customWidth="true" width="13.1796875"/>
+    <col min="2" max="2" customWidth="true" width="23.81640625"/>
+    <col min="3" max="3" customWidth="true" width="12.6328125"/>
+    <col min="6" max="6" customWidth="true" width="23.1796875"/>
+    <col min="7" max="7" customWidth="true" width="13.1796875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="D1" t="s" s="0">
-        <v>1</v>
-      </c>
       <c r="E1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1">
+      <c r="C2" s="1">
         <v>12</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>31</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>274</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="G2" t="s" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
         <v>10</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>294</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s" s="0">
+      <c r="G3" t="s" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="1">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1">
         <v>934</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s" s="0">
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>4</v>
       </c>
     </row>
@@ -749,42 +778,54 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E14915E-E896-4209-8E48-035EA63E22E1}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="16.1796875"/>
-    <col min="2" max="2" customWidth="true" width="36.90625"/>
+    <col min="2" max="2" customWidth="true" width="16.1796875"/>
+    <col min="3" max="3" customWidth="true" width="36.90625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B4" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1">
         <v>1</v>
       </c>
     </row>
@@ -792,49 +833,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8EAE46-4B76-4386-9505-380624A1252D}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" customWidth="true" width="22.54296875"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SathishReddy Sandhi\SeleniumAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCED712A-2653-4074-940B-E9F8AF2C7DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE11E0E-5EB0-4F68-B10B-5B7ED163C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="36">
   <si>
     <t>ProductName</t>
   </si>
@@ -103,7 +103,28 @@
     <t>Clothes</t>
   </si>
   <si>
-    <t>E2ETest</t>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>TC_01_iphone 13 pro</t>
+  </si>
+  <si>
+    <t>TC_02_ZARACOAT3</t>
+  </si>
+  <si>
+    <t>TC_03_Clothes</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Login.login</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>Completed Execution</t>
@@ -112,19 +133,10 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>Run</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>TC_01_iphone 13 pro</t>
-  </si>
-  <si>
-    <t>TC_02_ZARACOAT3</t>
-  </si>
-  <si>
-    <t>TC_03_Clothes</t>
+    <t>Skipped Execution</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
 </sst>
 </file>
@@ -144,7 +156,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,12 +165,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="none">
-        <fgColor indexed="17"/>
+        <fgColor indexed="13"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="13"/>
       </patternFill>
     </fill>
   </fills>
@@ -174,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -185,11 +217,13 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
@@ -471,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4687A51-E3F6-4959-AD9A-99F0B4444C26}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="29.90625"/>
@@ -493,44 +527,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s" s="10">
-        <v>26</v>
-      </c>
-      <c r="D2" s="11" t="n">
-        <v>46107.58985373843</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s" s="12">
-        <v>26</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>46107.590114976854</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s" s="14">
-        <v>26</v>
-      </c>
-      <c r="D4" s="15" t="n">
-        <v>46107.59039252315</v>
+        <v>32</v>
+      </c>
+      <c r="C2" t="s" s="16">
+        <v>33</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>46107.80262769676</v>
       </c>
     </row>
   </sheetData>
@@ -553,7 +559,7 @@
         <v>18</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>0</v>
@@ -564,10 +570,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>22</v>
@@ -578,10 +584,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>17</v>
@@ -592,10 +598,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>31</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>28</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>23</v>
@@ -631,7 +637,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>22</v>
@@ -642,7 +648,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>17</v>
@@ -653,7 +659,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>23</v>
@@ -704,7 +710,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -727,7 +733,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
@@ -750,7 +756,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>14</v>
@@ -798,7 +804,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>22</v>
@@ -809,7 +815,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>23</v>
@@ -820,7 +826,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>17</v>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="36">
   <si>
     <t>ProductName</t>
   </si>
@@ -206,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -220,6 +220,30 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -532,11 +556,11 @@
       <c r="B2" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C2" t="s" s="16">
+      <c r="C2" t="s" s="40">
         <v>33</v>
       </c>
-      <c r="D2" s="17" t="n">
-        <v>46107.80262769676</v>
+      <c r="D2" s="41" t="n">
+        <v>46107.8422228125</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SathishReddy Sandhi\SeleniumAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE11E0E-5EB0-4F68-B10B-5B7ED163C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9293C33-5BCD-4284-BB6B-8C072A232E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="8" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="37">
   <si>
     <t>ProductName</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Country</t>
   </si>
   <si>
-    <t>Sathish Reddy</t>
-  </si>
-  <si>
     <t>India</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
     <t>ExpectedQty</t>
   </si>
   <si>
-    <t>Sathish Reddy Sandhi</t>
-  </si>
-  <si>
     <t>1234567898765432</t>
   </si>
   <si>
@@ -79,73 +73,81 @@
     <t>06</t>
   </si>
   <si>
+    <t>ZARA COAT 3</t>
+  </si>
+  <si>
+    <t>TestCaseName</t>
+  </si>
+  <si>
+    <t>StepName</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>iphone 13 pro</t>
+  </si>
+  <si>
+    <t>Clothes</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>TC_01_iphone 13 pro</t>
+  </si>
+  <si>
+    <t>TC_02_ZARACOAT3</t>
+  </si>
+  <si>
+    <t>TC_03_Clothes</t>
+  </si>
+  <si>
+    <t>Completed Execution</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sathish Reddy </t>
+  </si>
+  <si>
     <t>Devender Reddy</t>
   </si>
   <si>
-    <t>ZARA COAT 3</t>
-  </si>
-  <si>
-    <t>TestCaseName</t>
-  </si>
-  <si>
-    <t>StepName</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>iphone 13 pro</t>
-  </si>
-  <si>
-    <t>Clothes</t>
-  </si>
-  <si>
-    <t>Run</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>TC_01_iphone 13 pro</t>
-  </si>
-  <si>
-    <t>TC_02_ZARACOAT3</t>
-  </si>
-  <si>
-    <t>TC_03_Clothes</t>
+    <t>Chandra Reddy</t>
+  </si>
+  <si>
+    <t>TC_04_ZARACOAT3</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Sulochana Reddy</t>
+  </si>
+  <si>
+    <t>Payment.validateShippingInfo</t>
   </si>
   <si>
     <t>FAIL</t>
   </si>
   <si>
-    <t>Login.login</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Completed Execution</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>Skipped Execution</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>Execution</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -156,7 +158,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,32 +167,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="13"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="13"/>
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -206,49 +188,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,38 +474,248 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4687A51-E3F6-4959-AD9A-99F0B4444C26}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="29.90625"/>
+    <col min="2" max="2" width="29.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s" s="40">
-        <v>33</v>
-      </c>
-      <c r="D2" s="41" t="n">
-        <v>46107.8422228125</v>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46111.726300902781</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46111.726327604163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46111.726339826389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46111.726340925925</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46111.735072685187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46111.735075543984</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2">
+        <v>46111.735078055557</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46111.735115601849</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46111.744067175925</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46111.744074768518</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="2">
+        <v>46111.744106238424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="2">
+        <v>46111.744107430553</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46112.649900208336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46112.649905902777</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46112.649919513889</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="2">
+        <v>46112.649925740741</v>
       </c>
     </row>
   </sheetData>
@@ -570,67 +725,81 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2D4A01-FD8A-4C00-8AEF-6100DA0E02DE}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="15.36328125"/>
-    <col min="3" max="3" customWidth="true" width="37.54296875"/>
-    <col min="4" max="4" customWidth="true" width="23.08984375"/>
+    <col min="1" max="1" width="33.36328125" customWidth="1"/>
+    <col min="3" max="3" width="37.54296875" customWidth="1"/>
+    <col min="4" max="4" width="23.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s" s="0">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="C1" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s" s="0">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="D4" s="0">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
     </row>
@@ -642,53 +811,65 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334CF848-C880-4642-954D-864DF5E51C2D}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" customWidth="true" width="19.90625"/>
+    <col min="1" max="1" width="19.7265625" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s" s="0">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s" s="0">
-        <v>5</v>
+      <c r="C1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="C2" s="0">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>17</v>
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C4" s="0">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1">
         <v>1</v>
       </c>
     </row>
@@ -700,44 +881,45 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2AF52E-5086-43AC-9E41-3304A02A9C8C}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="23.81640625"/>
-    <col min="3" max="3" customWidth="true" width="12.6328125"/>
-    <col min="6" max="6" customWidth="true" width="23.1796875"/>
-    <col min="7" max="7" customWidth="true" width="13.1796875"/>
+    <col min="1" max="1" width="42.08984375" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" customWidth="1"/>
+    <col min="6" max="6" width="23.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s" s="0">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>26</v>
+      <c r="A2" t="s">
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>12</v>
@@ -749,21 +931,21 @@
         <v>274</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>27</v>
+      <c r="A3" t="s">
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
@@ -772,21 +954,21 @@
         <v>294</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>28</v>
+      <c r="A4" t="s">
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1">
         <v>15</v>
@@ -795,10 +977,33 @@
         <v>934</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1">
+        <v>594</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -808,54 +1013,65 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E14915E-E896-4209-8E48-035EA63E22E1}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="16.1796875"/>
-    <col min="3" max="3" customWidth="true" width="36.90625"/>
+    <col min="2" max="2" width="16.1796875" customWidth="1"/>
+    <col min="3" max="3" width="36.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s" s="0">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s" s="0">
-        <v>10</v>
+      <c r="C1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="C2" s="0">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C3" s="0">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>17</v>
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
       </c>
       <c r="C4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1">
         <v>1</v>
       </c>
     </row>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SathishReddy Sandhi\SeleniumAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9293C33-5BCD-4284-BB6B-8C072A232E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C05501-B04A-4E83-AE8A-CD85389FC200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="8" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="60">
   <si>
     <t>ProductName</t>
   </si>
@@ -109,45 +109,115 @@
     <t>TC_03_Clothes</t>
   </si>
   <si>
+    <t xml:space="preserve">Sathish Reddy </t>
+  </si>
+  <si>
+    <t>Devender Reddy</t>
+  </si>
+  <si>
+    <t>Chandra Reddy</t>
+  </si>
+  <si>
+    <t>TC_04_ZARACOAT3</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Sulochana Reddy</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Order.CheckOrderConfirmed</t>
+  </si>
+  <si>
+    <t>Cart.isProductInCart</t>
+  </si>
+  <si>
+    <t>2026-04-01 15:57:16</t>
+  </si>
+  <si>
+    <t>2026-04-01 15:57:21</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:02:56</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:02:58</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:03:01</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:04:14</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:04:18</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:04:19</t>
+  </si>
+  <si>
     <t>Completed Execution</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t xml:space="preserve">Sathish Reddy </t>
-  </si>
-  <si>
-    <t>Devender Reddy</t>
-  </si>
-  <si>
-    <t>Chandra Reddy</t>
-  </si>
-  <si>
-    <t>TC_04_ZARACOAT3</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>Sulochana Reddy</t>
-  </si>
-  <si>
-    <t>Payment.validateShippingInfo</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>Execution</t>
+    <t>2026-04-01 16:05:27</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:05:28</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:05:29</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:08:44</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:08:45</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:20:00</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:20:01</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:20:02</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:31:25</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:31:26</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:32:10</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:32:14</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:32:16</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:33:24</t>
+  </si>
+  <si>
+    <t>2026-04-01 16:33:25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -158,7 +228,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -171,8 +241,18 @@
       </patternFill>
     </fill>
     <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
       </patternFill>
     </fill>
   </fills>
@@ -188,12 +268,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,248 +585,587 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4687A51-E3F6-4959-AD9A-99F0B4444C26}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.90625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="44.7265625"/>
+    <col min="2" max="2" customWidth="true" width="55.90625"/>
+    <col min="3" max="3" customWidth="true" width="11.453125"/>
+    <col min="4" max="4" customWidth="true" width="63.26953125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="2">
-        <v>46111.726300902781</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46111.726327604163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46111.726339826389</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B7" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46111.726340925925</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46111.735072685187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B13" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B15" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46111.735075543984</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="C26" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="2">
-        <v>46111.735078055557</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B28" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46111.735115601849</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B29" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="2">
-        <v>46111.744067175925</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="2">
-        <v>46111.744074768518</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B31" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="2">
-        <v>46111.744106238424</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B33" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="2">
-        <v>46111.744107430553</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="B36" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C38" t="s" s="28">
+        <v>44</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <v>46113.69025582176</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C39" t="s" s="30">
+        <v>44</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>46113.690267858794</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="2">
-        <v>46112.649900208336</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="2">
-        <v>46112.649905902777</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="2">
-        <v>46112.649919513889</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="B40" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C40" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="D40" s="33" t="n">
+        <v>46113.690277407404</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="2">
-        <v>46112.649925740741</v>
+      <c r="B41" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C41" t="s" s="34">
+        <v>44</v>
+      </c>
+      <c r="D41" s="35" t="n">
+        <v>46113.690287453705</v>
       </c>
     </row>
   </sheetData>
@@ -728,47 +1178,47 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.36328125" customWidth="1"/>
-    <col min="3" max="3" width="37.54296875" customWidth="1"/>
-    <col min="4" max="4" width="23.08984375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="33.36328125"/>
+    <col min="3" max="3" customWidth="true" width="37.54296875"/>
+    <col min="4" max="4" customWidth="true" width="23.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>14</v>
       </c>
       <c r="D3" s="1">
@@ -776,27 +1226,27 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>14</v>
       </c>
       <c r="D5" s="1">
@@ -814,37 +1264,37 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" customWidth="1"/>
-    <col min="3" max="3" width="19.90625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="19.7265625"/>
+    <col min="3" max="3" customWidth="true" width="19.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>14</v>
       </c>
       <c r="C3" s="1">
@@ -852,21 +1302,21 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>14</v>
       </c>
       <c r="C5" s="1">
@@ -884,38 +1334,38 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.08984375" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" customWidth="1"/>
-    <col min="6" max="6" width="23.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="42.08984375"/>
+    <col min="2" max="2" customWidth="true" width="23.81640625"/>
+    <col min="3" max="3" customWidth="true" width="12.6328125"/>
+    <col min="6" max="6" customWidth="true" width="23.1796875"/>
+    <col min="7" max="7" customWidth="true" width="13.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -931,14 +1381,14 @@
         <v>274</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s" s="0">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -954,14 +1404,14 @@
         <v>294</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s" s="0">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -977,21 +1427,21 @@
         <v>934</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>31</v>
+      <c r="A5" t="s" s="0">
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1">
         <v>27</v>
@@ -1000,9 +1450,9 @@
         <v>594</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>3</v>
       </c>
     </row>
@@ -1016,48 +1466,48 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="16.1796875" customWidth="1"/>
-    <col min="3" max="3" width="36.90625" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="16.1796875"/>
+    <col min="3" max="3" customWidth="true" width="36.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>14</v>
       </c>
       <c r="C4" s="1">
@@ -1065,10 +1515,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>14</v>
       </c>
       <c r="C5" s="1">

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SathishReddy Sandhi\SeleniumAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C05501-B04A-4E83-AE8A-CD85389FC200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7ABFCF-3C7C-4167-99B8-45114F9B8B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="62">
   <si>
     <t>ProductName</t>
   </si>
@@ -79,6 +79,45 @@
     <t>TestCaseName</t>
   </si>
   <si>
+    <t>iphone 13 pro</t>
+  </si>
+  <si>
+    <t>Clothes</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>TC_01_iphone 13 pro</t>
+  </si>
+  <si>
+    <t>TC_02_ZARACOAT3</t>
+  </si>
+  <si>
+    <t>TC_03_Clothes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sathish Reddy </t>
+  </si>
+  <si>
+    <t>Devender Reddy</t>
+  </si>
+  <si>
+    <t>Chandra Reddy</t>
+  </si>
+  <si>
+    <t>TC_04_ZARACOAT3</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Sulochana Reddy</t>
+  </si>
+  <si>
     <t>StepName</t>
   </si>
   <si>
@@ -88,127 +127,94 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>iphone 13 pro</t>
-  </si>
-  <si>
-    <t>Clothes</t>
-  </si>
-  <si>
-    <t>Run</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>TC_01_iphone 13 pro</t>
-  </si>
-  <si>
-    <t>TC_02_ZARACOAT3</t>
-  </si>
-  <si>
-    <t>TC_03_Clothes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sathish Reddy </t>
-  </si>
-  <si>
-    <t>Devender Reddy</t>
-  </si>
-  <si>
-    <t>Chandra Reddy</t>
-  </si>
-  <si>
-    <t>TC_04_ZARACOAT3</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>Sulochana Reddy</t>
+    <t>Completed Execution</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:07:20</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:07:21</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:08:20</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:08:21</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:08:22</t>
+  </si>
+  <si>
+    <t>Order.validateProductName</t>
   </si>
   <si>
     <t>FAIL</t>
   </si>
   <si>
-    <t>Order.CheckOrderConfirmed</t>
+    <t>2026-04-01 18:09:14</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:09:15</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:09:16</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:10:35</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:10:36</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:10:37</t>
   </si>
   <si>
     <t>Cart.isProductInCart</t>
   </si>
   <si>
-    <t>2026-04-01 15:57:16</t>
-  </si>
-  <si>
-    <t>2026-04-01 15:57:21</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:02:56</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:02:58</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:03:01</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:04:14</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:04:18</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:04:19</t>
-  </si>
-  <si>
-    <t>Completed Execution</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:05:27</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:05:28</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:05:29</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:08:44</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:08:45</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:20:00</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:20:01</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:20:02</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:31:25</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:31:26</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:32:10</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:32:14</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:32:16</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:33:24</t>
-  </si>
-  <si>
-    <t>2026-04-01 16:33:25</t>
+    <t>2026-04-01 18:14:57</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:14:58</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:16:44</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:16:46</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:17:21</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:17:30</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:17:33</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:18:33</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:18:41</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:18:42</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:18:45</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:19:37</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:19:45</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:19:46</t>
   </si>
 </sst>
 </file>
@@ -241,11 +247,6 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor indexed="10"/>
       </patternFill>
@@ -253,6 +254,11 @@
     <fill>
       <patternFill patternType="none">
         <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -268,43 +274,174 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,38 +736,38 @@
         <v>15</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>35</v>
@@ -638,55 +775,55 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>37</v>
@@ -694,153 +831,153 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s" s="0">
         <v>44</v>
-      </c>
-      <c r="D14" t="s" s="0">
-        <v>45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>48</v>
@@ -848,13 +985,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>48</v>
@@ -862,27 +999,27 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>49</v>
@@ -890,13 +1027,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>50</v>
@@ -904,27 +1041,27 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>51</v>
@@ -932,41 +1069,41 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>53</v>
@@ -974,13 +1111,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>53</v>
@@ -988,13 +1125,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>54</v>
@@ -1002,13 +1139,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>55</v>
@@ -1016,13 +1153,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>56</v>
@@ -1030,142 +1167,142 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="C38" t="s" s="28">
-        <v>44</v>
-      </c>
-      <c r="D38" s="29" t="n">
-        <v>46113.69025582176</v>
+        <v>32</v>
+      </c>
+      <c r="C38" t="s" s="77">
+        <v>33</v>
+      </c>
+      <c r="D38" s="78" t="n">
+        <v>46113.76476164352</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="C39" t="s" s="30">
-        <v>44</v>
-      </c>
-      <c r="D39" s="31" t="n">
-        <v>46113.690267858794</v>
+        <v>32</v>
+      </c>
+      <c r="C39" t="s" s="79">
+        <v>33</v>
+      </c>
+      <c r="D39" s="80" t="n">
+        <v>46113.76476266204</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="C40" t="s" s="32">
-        <v>44</v>
-      </c>
-      <c r="D40" s="33" t="n">
-        <v>46113.690277407404</v>
+        <v>32</v>
+      </c>
+      <c r="C40" t="s" s="81">
+        <v>33</v>
+      </c>
+      <c r="D40" s="82" t="n">
+        <v>46113.7647705787</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="C41" t="s" s="34">
-        <v>44</v>
-      </c>
-      <c r="D41" s="35" t="n">
-        <v>46113.690287453705</v>
+        <v>32</v>
+      </c>
+      <c r="C41" t="s" s="83">
+        <v>33</v>
+      </c>
+      <c r="D41" s="84" t="n">
+        <v>46113.76477175926</v>
       </c>
     </row>
   </sheetData>
@@ -1188,7 +1325,7 @@
         <v>15</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>0</v>
@@ -1199,13 +1336,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D2" s="0">
         <v>1</v>
@@ -1213,10 +1350,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>14</v>
@@ -1227,13 +1364,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D4" s="0">
         <v>1</v>
@@ -1241,10 +1378,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>14</v>
@@ -1281,10 +1418,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" s="0">
         <v>1</v>
@@ -1292,7 +1429,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>14</v>
@@ -1303,10 +1440,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" s="0">
         <v>1</v>
@@ -1314,7 +1451,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>14</v>
@@ -1366,7 +1503,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
@@ -1381,7 +1518,7 @@
         <v>274</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>3</v>
@@ -1389,7 +1526,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>10</v>
@@ -1404,7 +1541,7 @@
         <v>294</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>3</v>
@@ -1412,7 +1549,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -1427,7 +1564,7 @@
         <v>934</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>3</v>
@@ -1435,13 +1572,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1">
         <v>27</v>
@@ -1450,7 +1587,7 @@
         <v>594</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>3</v>
@@ -1466,6 +1603,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" customWidth="true" width="34.6328125"/>
     <col min="2" max="2" customWidth="true" width="16.1796875"/>
     <col min="3" max="3" customWidth="true" width="36.90625"/>
   </cols>
@@ -1483,10 +1621,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" s="0">
         <v>1</v>
@@ -1494,10 +1632,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C3" s="0">
         <v>1</v>
@@ -1505,10 +1643,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -1516,7 +1654,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>14</v>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="68">
   <si>
     <t>ProductName</t>
   </si>
@@ -215,6 +215,24 @@
   </si>
   <si>
     <t>2026-04-01 18:19:46</t>
+  </si>
+  <si>
+    <t>2026-04-02 09:59:18</t>
+  </si>
+  <si>
+    <t>2026-04-02 09:59:19</t>
+  </si>
+  <si>
+    <t>2026-04-02 09:59:20</t>
+  </si>
+  <si>
+    <t>2026-04-02 09:59:21</t>
+  </si>
+  <si>
+    <t>2026-04-02 10:00:54</t>
+  </si>
+  <si>
+    <t>2026-04-02 10:00:55</t>
   </si>
 </sst>
 </file>
@@ -274,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -411,6 +429,62 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
@@ -722,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4687A51-E3F6-4959-AD9A-99F0B4444C26}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="44.7265625"/>
@@ -756,12 +830,12 @@
         <v>33</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>32</v>
@@ -770,12 +844,12 @@
         <v>33</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>32</v>
@@ -784,12 +858,12 @@
         <v>33</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>32</v>
@@ -798,7 +872,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -812,12 +886,12 @@
         <v>33</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>32</v>
@@ -826,12 +900,12 @@
         <v>33</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>32</v>
@@ -840,12 +914,12 @@
         <v>33</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>32</v>
@@ -854,35 +928,35 @@
         <v>33</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C10" t="s" s="0">
+      <c r="C10" t="s" s="101">
         <v>33</v>
       </c>
-      <c r="D10" t="s" s="0">
-        <v>41</v>
+      <c r="D10" s="102" t="n">
+        <v>46114.66805201389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="C11" t="s" s="103">
+        <v>33</v>
+      </c>
+      <c r="D11" s="104" t="n">
+        <v>46114.66807357639</v>
       </c>
     </row>
     <row r="12">
@@ -892,417 +966,53 @@
       <c r="B12" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C12" t="s" s="0">
+      <c r="C12" t="s" s="105">
         <v>33</v>
       </c>
-      <c r="D12" t="s" s="0">
-        <v>43</v>
+      <c r="D12" s="106" t="n">
+        <v>46114.66808581018</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C13" t="s" s="0">
+      <c r="C13" t="s" s="107">
         <v>33</v>
       </c>
-      <c r="D13" t="s" s="0">
-        <v>43</v>
+      <c r="D13" s="108" t="n">
+        <v>46114.66808902778</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C14" t="s" s="0">
+      <c r="C14" t="s" s="109">
         <v>33</v>
       </c>
-      <c r="D14" t="s" s="0">
-        <v>44</v>
+      <c r="D14" s="110" t="n">
+        <v>46114.66809615741</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C15" t="s" s="0">
+      <c r="C15" t="s" s="111">
         <v>33</v>
       </c>
-      <c r="D15" t="s" s="0">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D21" t="s" s="0">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D22" t="s" s="0">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D23" t="s" s="0">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D24" t="s" s="0">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D25" t="s" s="0">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="C26" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D26" t="s" s="0">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D27" t="s" s="0">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D28" t="s" s="0">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C29" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D29" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B30" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="C30" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D30" t="s" s="0">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D31" t="s" s="0">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="C32" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D32" t="s" s="0">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C33" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D33" t="s" s="0">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B34" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="C34" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D34" t="s" s="0">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B35" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C35" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D35" t="s" s="0">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B36" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C36" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D36" t="s" s="0">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B37" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C37" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D37" t="s" s="0">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B38" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C38" t="s" s="77">
-        <v>33</v>
-      </c>
-      <c r="D38" s="78" t="n">
-        <v>46113.76476164352</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B39" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C39" t="s" s="79">
-        <v>33</v>
-      </c>
-      <c r="D39" s="80" t="n">
-        <v>46113.76476266204</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B40" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C40" t="s" s="81">
-        <v>33</v>
-      </c>
-      <c r="D40" s="82" t="n">
-        <v>46113.7647705787</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C41" t="s" s="83">
-        <v>33</v>
-      </c>
-      <c r="D41" s="84" t="n">
-        <v>46113.76477175926</v>
+      <c r="D15" s="112" t="n">
+        <v>46114.66809886574</v>
       </c>
     </row>
   </sheetData>
